--- a/spreadsheet/macrofree/wafsg_checklist.es.xlsx
+++ b/spreadsheet/macrofree/wafsg_checklist.es.xlsx
@@ -2831,7 +2831,11 @@
     <row r="65" ht="16.5" customHeight="1">
       <c r="A65" s="21" t="n"/>
       <c r="B65" s="21" t="n"/>
-      <c r="C65" s="21" t="n"/>
+      <c r="C65" s="21" t="inlineStr">
+        <is>
+          <t>Habilite la opción AlwaysOn cuando las aplicaciones compartan un único plan de App Service. Las aplicaciones de App Service se descargan automáticamente cuando están inactivas para ahorrar recursos. La siguiente solicitud desencadena un inicio en frío, lo que puede provocar tiempos de espera de solicitud.</t>
+        </is>
+      </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
           <t>La aplicación nunca se descarga con Always On habilitado.</t>
@@ -2984,7 +2988,11 @@
     <row r="70" ht="16.5" customHeight="1">
       <c r="A70" s="21" t="n"/>
       <c r="B70" s="21" t="n"/>
-      <c r="C70" s="21" t="n"/>
+      <c r="C70" s="21" t="inlineStr">
+        <is>
+          <t>Planear las actualizaciones de las reglas</t>
+        </is>
+      </c>
       <c r="D70" s="21" t="inlineStr"/>
       <c r="E70" s="21" t="n"/>
       <c r="F70" t="inlineStr">
@@ -3015,7 +3023,7 @@
           <t>Uso de sondeos de estado para detectar la falta de disponibilidad del back-end</t>
         </is>
       </c>
-      <c r="D71" s="21" t="n"/>
+      <c r="D71" s="21" t="inlineStr"/>
       <c r="E71" s="21" t="n"/>
       <c r="F71" t="inlineStr">
         <is>
@@ -3075,7 +3083,7 @@
           <t>Comprobación de las dependencias de nivel inferior a través de puntos de conexión de estado</t>
         </is>
       </c>
-      <c r="D73" s="21" t="n"/>
+      <c r="D73" s="21" t="inlineStr"/>
       <c r="E73" s="21" t="n"/>
       <c r="F73" t="inlineStr">
         <is>
@@ -3207,7 +3215,11 @@
           <t>Comprobación de las dependencias de nivel inferior a través de puntos de conexión de estado</t>
         </is>
       </c>
-      <c r="D77" s="21" t="n"/>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>Supongamos que cada backend tiene sus propias dependencias para garantizar que se aíslen los errores. Por ejemplo, una aplicación hospedada detrás de Application Gateway puede tener varios back-ends, cada uno conectado a una base de datos diferente (réplica). Cuando se produce un error en una dependencia de este tipo, es posible que la aplicación esté funcionando, pero no devolverá resultados válidos. Por ese motivo, lo ideal es que el punto de conexión de mantenimiento valide todas las dependencias. Tenga en cuenta que si cada llamada al punto de conexión de estado tiene una llamada de dependencia directa, esa base de datos recibiría 100 consultas cada 30 segundos en lugar de 1. Para evitar esto, el punto de conexión de mantenimiento debe almacenar en caché el estado de las dependencias durante un breve período de tiempo.</t>
+        </is>
+      </c>
       <c r="E77" s="21" t="n"/>
       <c r="F77" t="inlineStr">
         <is>
@@ -12595,6 +12607,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Arquitectura de clúster: autentique con el identificador de Microsoft Entra en Azure Container Registry.</t>
+        </is>
+      </c>
       <c r="D431" t="inlineStr">
         <is>
           <t>AKS y Microsoft Entra ID habilitan la autenticación con Azure Container Registry sin el uso de secretos 'imagePullSecrets'. Para obtener más información, consulte Autenticación con Azure Container Registry de Azure Kubernetes Service.</t>
@@ -12868,6 +12885,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Arquitectura de clúster: revise las métricas de rendimiento, empezando por la CPU, la memoria, el almacenamiento y la red, para identificar las oportunidades de optimización de costos por clúster, nodos y espacio de nombres.</t>
+        </is>
+      </c>
       <c r="D444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>

--- a/spreadsheet/macrofree/wafsg_checklist.es.xlsx
+++ b/spreadsheet/macrofree/wafsg_checklist.es.xlsx
@@ -2831,7 +2831,11 @@
     <row r="65" ht="16.5" customHeight="1">
       <c r="A65" s="21" t="n"/>
       <c r="B65" s="21" t="n"/>
-      <c r="C65" s="21" t="n"/>
+      <c r="C65" s="21" t="inlineStr">
+        <is>
+          <t>Habilite la opción AlwaysOn cuando las aplicaciones compartan un único plan de App Service. Las aplicaciones de App Service se descargan automáticamente cuando están inactivas para ahorrar recursos. La siguiente solicitud desencadena un inicio en frío, lo que puede provocar tiempos de espera de solicitud.</t>
+        </is>
+      </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
           <t>La aplicación nunca se descarga con Always On habilitado.</t>
@@ -2984,7 +2988,11 @@
     <row r="70" ht="16.5" customHeight="1">
       <c r="A70" s="21" t="n"/>
       <c r="B70" s="21" t="n"/>
-      <c r="C70" s="21" t="n"/>
+      <c r="C70" s="21" t="inlineStr">
+        <is>
+          <t>Planear las actualizaciones de las reglas</t>
+        </is>
+      </c>
       <c r="D70" s="21" t="inlineStr"/>
       <c r="E70" s="21" t="n"/>
       <c r="F70" t="inlineStr">
@@ -3015,7 +3023,7 @@
           <t>Uso de sondeos de estado para detectar la falta de disponibilidad del back-end</t>
         </is>
       </c>
-      <c r="D71" s="21" t="n"/>
+      <c r="D71" s="21" t="inlineStr"/>
       <c r="E71" s="21" t="n"/>
       <c r="F71" t="inlineStr">
         <is>
@@ -3075,7 +3083,7 @@
           <t>Comprobación de las dependencias de nivel inferior a través de puntos de conexión de estado</t>
         </is>
       </c>
-      <c r="D73" s="21" t="n"/>
+      <c r="D73" s="21" t="inlineStr"/>
       <c r="E73" s="21" t="n"/>
       <c r="F73" t="inlineStr">
         <is>
@@ -3207,7 +3215,11 @@
           <t>Comprobación de las dependencias de nivel inferior a través de puntos de conexión de estado</t>
         </is>
       </c>
-      <c r="D77" s="21" t="n"/>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>Supongamos que cada backend tiene sus propias dependencias para garantizar que se aíslen los errores. Por ejemplo, una aplicación hospedada detrás de Application Gateway puede tener varios back-ends, cada uno conectado a una base de datos diferente (réplica). Cuando se produce un error en una dependencia de este tipo, es posible que la aplicación esté funcionando, pero no devolverá resultados válidos. Por ese motivo, lo ideal es que el punto de conexión de mantenimiento valide todas las dependencias. Tenga en cuenta que si cada llamada al punto de conexión de estado tiene una llamada de dependencia directa, esa base de datos recibiría 100 consultas cada 30 segundos en lugar de 1. Para evitar esto, el punto de conexión de mantenimiento debe almacenar en caché el estado de las dependencias durante un breve período de tiempo.</t>
+        </is>
+      </c>
       <c r="E77" s="21" t="n"/>
       <c r="F77" t="inlineStr">
         <is>
@@ -11096,11 +11108,6 @@
           <t>Evalúe el impacto en el rendimiento de IDPS en modo de alerta y denegación. Para más información, consulte Rendimiento de Azure Firewall.</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>Habilite IDPS en modo de alerta y denegación para detectar y prevenir actividades maliciosas en la red. Esta característica podría introducir una penalización del rendimiento. Comprenda el efecto en su carga de trabajo para que pueda planificar en consecuencia.</t>
-        </is>
-      </c>
       <c r="F355" t="inlineStr">
         <is>
           <t>No verificado</t>
@@ -11230,7 +11237,6 @@
           <t>Considere una opción de administración de tráfico redundante. Azure Front Door es un servicio distribuido globalmente que se ejecuta como un singleton en un entorno. Azure Front Door es un posible punto único de error en el sistema. Si se produce un error en el servicio, los clientes no podrán acceder a la aplicación durante el tiempo de inactividad.</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>No verificado</t>
@@ -11270,11 +11276,6 @@
           <t>Compatibilidad con la redundancia al tener varios orígenes en uno o varios grupos de back-end. Tenga siempre instancias redundantes de su aplicación y asegúrese de que cada instancia exponga un punto de conexión u origen. Puede colocar esos orígenes en uno o varios grupos de back-end.</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>Varios orígenes admiten redundancia mediante la distribución del tráfico entre varias instancias de la aplicación. Si una instancia no está disponible, otros orígenes de back-end aún pueden recibir tráfico.</t>
-        </is>
-      </c>
       <c r="F364" t="inlineStr">
         <is>
           <t>No verificado</t>
@@ -11375,11 +11376,6 @@
       </c>
     </row>
     <row r="369">
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Aproveche las reglas de limitación de velocidad que se incluyen con un firewall de aplicaciones web (WAF).</t>
-        </is>
-      </c>
       <c r="D369" t="inlineStr">
         <is>
           <t>Limite las solicitudes para evitar que los clientes envíen demasiado tráfico a la aplicación. La limitación de velocidad puede ayudarte a evitar problemas como una tormenta de reintentos.</t>
@@ -11415,11 +11411,6 @@
       </c>
     </row>
     <row r="371">
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Proteja los servidores back-end. El front-end actúa como el único punto de entrada a la aplicación.</t>
-        </is>
-      </c>
       <c r="D371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
@@ -11469,11 +11460,6 @@
       </c>
     </row>
     <row r="374">
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>Proteja Azure Front Door frente al tráfico inesperado. Azure Front Door usa el plan básico de protección contra DDoS de Azure para proteger los puntos de conexión de las aplicaciones frente a ataques DDoS. Si necesita exponer otras direcciones IP públicas de su aplicación, considere la posibilidad de agregar el plan estándar DDoS Protection para esas direcciones para capacidades avanzadas de protección y detección.</t>
-        </is>
-      </c>
       <c r="D374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
@@ -11786,7 +11772,6 @@
           <t>Simplifique las configuraciones. Use Azure Front Door para administrar fácilmente las configuraciones. Por ejemplo, supongamos que la arquitectura admite microservicios. Azure Front Door admite funcionalidades de redireccionamiento, por lo que puede usar el redireccionamiento basado en rutas de acceso para dirigirse a servicios individuales.</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
           <t>No verificado</t>
@@ -12595,6 +12580,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Arquitectura de clúster: autentique con el identificador de Microsoft Entra en Azure Container Registry.</t>
+        </is>
+      </c>
       <c r="D431" t="inlineStr">
         <is>
           <t>AKS y Microsoft Entra ID habilitan la autenticación con Azure Container Registry sin el uso de secretos 'imagePullSecrets'. Para obtener más información, consulte Autenticación con Azure Container Registry de Azure Kubernetes Service.</t>
@@ -12868,6 +12858,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Arquitectura de clúster: revise las métricas de rendimiento, empezando por la CPU, la memoria, el almacenamiento y la red, para identificar las oportunidades de optimización de costos por clúster, nodos y espacio de nombres.</t>
+        </is>
+      </c>
       <c r="D444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
